--- a/Result/profitability/1312.xlsx
+++ b/Result/profitability/1312.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.12</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.72</v>
+        <v>-0.74625</v>
       </c>
       <c r="N2" t="n">
-        <v>-2.7375</v>
+        <v>-2.69125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>-0.03</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6875</v>
+        <v>-0.69375</v>
       </c>
       <c r="N3" t="n">
-        <v>-2.01</v>
+        <v>-2.105</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>-0.11</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.645</v>
+        <v>-0.63</v>
       </c>
       <c r="N4" t="n">
-        <v>-2.18</v>
+        <v>-1.64125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-3.25</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.9737500000000001</v>
+        <v>-0.9225000000000001</v>
       </c>
       <c r="N5" t="n">
-        <v>-7.193750000000001</v>
+        <v>-6.02875</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.97</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.73875</v>
+        <v>-0.635</v>
       </c>
       <c r="N6" t="n">
-        <v>-3.950000000000001</v>
+        <v>-1.96</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>1.28</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4125</v>
+        <v>-0.33625</v>
       </c>
       <c r="N7" t="n">
-        <v>0.1274999999999991</v>
+        <v>1.063749999999999</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.92</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1587499999999999</v>
+        <v>-0.07499999999999997</v>
       </c>
       <c r="N8" t="n">
-        <v>2.326249999999999</v>
+        <v>2.7925</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1312</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>5397</v>
+      </c>
+      <c r="D75" t="n">
+        <v>5289</v>
+      </c>
+      <c r="E75" t="n">
+        <v>108</v>
+      </c>
+      <c r="F75" t="n">
+        <v>2</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-547</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-10.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-22</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-568</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-562</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.7975</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-3.0475</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.6699999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.5726495726495726</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.73</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-2.15606936416185</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.4505494505494506</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.273224043715847</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
